--- a/course-design-2/outputs/tables/ch7/34_temporal_split_results.xlsx
+++ b/course-design-2/outputs/tables/ch7/34_temporal_split_results.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_三划分对照" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Temporal主模型结果" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Temporal_Unseen" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_方法与口径" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_方法与统计范围" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/course-design-2/outputs/tables/ch7/34_temporal_split_results.xlsx
+++ b/course-design-2/outputs/tables/ch7/34_temporal_split_results.xlsx
@@ -595,7 +595,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阈值口径</t>
+          <t>阈值设定</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -652,7 +652,6 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -677,7 +676,6 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -702,7 +700,6 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -727,12 +724,8 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>351</v>
       </c>
@@ -749,9 +742,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>367</v>
       </c>
@@ -768,9 +758,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>399</v>
       </c>
@@ -1058,7 +1045,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1100,8 +1087,6 @@
           <t>同一协议：仅在 random train 上拟合估计器；与既有正式主模型同一测试集</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1168,8 +1153,6 @@
           <t>同一协议：仅使用时间上最早的约 70%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1199,8 +1182,6 @@
           <t>与 Stage25 正式主模型协议一致</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1230,8 +1211,6 @@
           <t>只读引用既有正式结果（30 号表 09）</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1261,8 +1240,6 @@
           <t>只读引用既有正式结果（31 号表 04）</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
